--- a/templates/吸附数据模板.xlsx
+++ b/templates/吸附数据模板.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sb(V) 吸附数据模板</t>
+          <t>吸附数据模板</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -531,7 +531,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>4. mineral 列直接填「英文名」（如 Rancieite、Acid birnessite）：图上就用这个名字，不再经脚本翻译。以后新增矿物，照这个写法填即可，不必改 names.json。</t>
+          <t>4. mineral 列直接填「英文名」（如 Mineral A、Goethite）：图上就用这个名字，不再经脚本翻译。以后新增吸附剂，照这个写法填即可，不必改 names.json。</t>
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
@@ -540,7 +540,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>5. Settings 表填全局默认值，并在 solids 区列出每个矿物的固液比 m/V (g/L)，键名与 mineral 列一致。</t>
+          <t>5. Settings 表填全局默认值；固液比 m/V (g/L) 可写在 Settings 的 solid:&lt;名称&gt; 行，也可逐行填在 Data 表。</t>
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
@@ -549,7 +549,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>6. 保存后执行：adsorp.bat run --template 吸附数据模板.xlsx --out output（在项目目录下；等价于 python -m adsorp.cli run）</t>
+          <t>6. 保存后执行：adsorp.bat run --template templates/吸附数据模板.xlsx --out output（在项目目录下；等价于 python -m adsorp.cli run）</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
@@ -558,7 +558,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>7. 结果：output/报告.html（含单图下载、每张图下方可展开的绘图代码）、结果汇总.xlsx、figures/（PNG+PDF）、tables/（CSV）。</t>
+          <t>7. 结果：output/报告.html（单文件自包含，图表与 PDF 均内嵌，可单独转发）、结果汇总.xlsx、figures/（PNG+PDF）、tables/（CSV）。</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -567,7 +567,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>8. 背景电解质写 NaNO3 或 NaNO₃ 都可以，脚本会统一成 NaNO₃ 再分组。</t>
+          <t>8. 背景电解质按字符串分组，写法要保持一致（如统一写 0.01 M NaCl）；全角/半角、上标下标的差异会被当成两组。</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -583,32 +583,32 @@
       <c r="C12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>10. 检查标准（QC）行单独写 exp=qc：标称 ppb 填 C0_ppm、测定 ppb 填 conc_ppb，mineral/background 可留空；脚本据此算回收率并出 QC 图。</t>
+        </is>
+      </c>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>浓度换算</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>11. Settings 的 molar_mass_g_per_mol / temperature_K 只用于 D-R 模型的吸附势换算；不填摩尔质量则跳过 D-R（其余等温线模型不受影响），换温度请同步改 temperature_K。</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>conc_ppb 填“标线计算/ppb”，不要填实测荧光值；若填 Ce_ppm，直接使用。</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>若只填 conc_ppb，则 Ce_ppm = conc_ppb × corr_factor × dilution / 1000。</t>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>浓度换算</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -617,7 +617,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>吸附率 (%) = 100 × (1 − Ce/C0)；qe (mg/g) = (C0 − Ce) / (m/V)。</t>
+          <t>conc_ppb 填“标线计算/ppb”，不要填实测荧光值；若填 Ce_ppm，直接使用。</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
@@ -626,293 +626,311 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>没有 Ce_ppm/conc_ppb 的行＝你已删掉或没做的点：静默跳过，不参与拟合与绘图。异常值脚本不替你处理，只在报告的数据质量清单里列出行号与建议。</t>
+          <t>若只填 conc_ppb，则 Ce_ppm = conc_ppb × corr_factor × dilution / 1000。</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>吸附率 (%) = 100 × (1 − Ce/C0)；qe (mg/g) = (C0 − Ce) / (m/V)。</t>
+        </is>
+      </c>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Data 表各列</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>没有 Ce_ppm/conc_ppb 的行＝你已删掉或没做的点：静默跳过，不参与拟合与绘图。异常值脚本不替你处理，只在报告的数据质量清单里列出行号与建议。</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>列名</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>示例</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>exp</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>isotherm | kinetics | edge</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>实验类型，三选一；同一实验块可只写首行，下面留空表示沿用上一行</t>
-        </is>
-      </c>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Data 表各列</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>mineral</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>δ-MnO₂ / Rancieite / …</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>矿物名，用英文（图上直接显示这个名字）；留空沿用上一行</t>
+          <t>列名</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>示例</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>background</t>
+          <t>exp</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>0.01 M NaNO₃ / ASW</t>
+          <t>isotherm | kinetics | edge | qc</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>背景电解质；留空沿用上一行</t>
+          <t>实验类型，四选一；qc 行用于检查标准（标称值填 C0_ppm、测定值填 conc_ppb）。同一实验块可只写首行，下面留空表示沿用上一行</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>ionic_strength_M</t>
+          <t>mineral</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>Mineral A / Mineral B</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>离子强度 (mol/L)，留空则从 background 解析</t>
+          <t>吸附剂名，用英文（图上直接显示这个名字）；留空沿用上一行</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>C0_ppm</t>
+          <t>background</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0.01 M NaCl / 0.1 M NaCl</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>初始 Sb(V) 浓度 (mg/L)；等温线必填，动力学/吸附边留空取默认</t>
+          <t>背景电解质；留空沿用上一行</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>time_h</t>
+          <t>ionic_strength_M</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>取样时间 (h)，仅 kinetics 必填；留空行会跳过</t>
+          <t>离子强度 (mol/L)，留空则从 background 解析</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>C0_ppm</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>平衡 pH，仅 edge 必填；留空行会跳过</t>
+          <t>初始浓度 (mg/L)；等温线必填，动力学/吸附边留空取默认</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Ce_ppm</t>
+          <t>time_h</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>平衡浓度 (mg/L)。有则优先使用</t>
+          <t>取样时间 (h)，仅 kinetics 必填；留空行会跳过</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>conc_ppb</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>标线计算/ppb（不是荧光值）。无 Ce_ppm 时按下方公式换算</t>
+          <t>平衡 pH，仅 edge 必填；留空行会跳过</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>corr_factor</t>
+          <t>Ce_ppm</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>校正因子（标线/漂移校正）</t>
+          <t>平衡浓度 (mg/L)。有则优先使用</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>dilution</t>
+          <t>conc_ppb</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>稀释倍数，留空取 Settings 默认值</t>
+          <t>标线计算/ppb（不是荧光值）。无 Ce_ppm 时按下方公式换算</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>solid_g_per_L</t>
+          <t>corr_factor</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>固液比 m/V。留空取 Settings 中该矿物的值</t>
+          <t>校正因子（标线/漂移校正）</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>replicate</t>
+          <t>dilution</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>平行样编号，可留空</t>
+          <t>稀释倍数，留空取 Settings 默认值</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>solid_g_per_L</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>异常，未加原液</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>备注；含 异常/存疑/加错/未取样/可疑/重测 的行自动剔除</t>
+          <t>固液比 m/V。留空取 Settings 中该矿物的值</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
+          <t>replicate</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>平行样编号，可留空</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>并行样 2</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>备注；含 异常/存疑/加错/未取样/可疑/重测 的行只提示，不自动剔除</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
           <t>exclude</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>唯一能剔除数据的开关：填 TRUE 则该行不参与拟合与绘图</t>
         </is>
@@ -929,7 +947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1034,34 +1052,34 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>δ-MnO₂</t>
+          <t>Mineral A</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>0.01 M NaNO₃</t>
+          <t>0.01 M NaCl</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="n">
-        <v>21.96</v>
+        <v>7.82</v>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1</v>
@@ -1079,34 +1097,34 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>δ-MnO₂</t>
+          <t>Mineral A</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>0.01 M NaNO₃</t>
+          <t>0.01 M NaCl</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="n">
-        <v>22.1</v>
+        <v>7.65</v>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>2</v>
@@ -1119,41 +1137,39 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>kinetics</t>
+          <t>isotherm</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Rancieite</t>
+          <t>Mineral B</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0.01 M NaNO₃</t>
+          <t>0.01 M NaCl</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>24</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="n">
-        <v>1.7</v>
-      </c>
+      <c r="H4" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>598.8889</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>1</v>
@@ -1166,47 +1182,94 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>edge</t>
+          <t>kinetics</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Acid birnessite</t>
+          <t>Mineral A</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0.01 M NaNO₃</t>
+          <t>0.01 M NaCl</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="n">
+        <v>102.4</v>
+      </c>
       <c r="J5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Mineral A</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1221,7 +1284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1248,7 +1311,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Sb(V) adsorption on Mn oxides</t>
+          <t>Adsorption dataset</t>
         </is>
       </c>
     </row>
@@ -1266,11 +1329,7 @@
           <t>analyte</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Sb(V)</t>
-        </is>
-      </c>
+      <c r="B4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1278,9 +1337,7 @@
           <t>molar_mass_g_per_mol</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>121.76</v>
-      </c>
+      <c r="B5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1298,9 +1355,7 @@
           <t>default_C0_kinetics</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="B7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1308,9 +1363,7 @@
           <t>default_C0_edge</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="B8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1318,9 +1371,7 @@
           <t>default_dilution_kinetics</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>600</v>
-      </c>
+      <c r="B9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1328,9 +1379,7 @@
           <t>default_dilution_edge</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>600</v>
-      </c>
+      <c r="B10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1338,9 +1387,7 @@
           <t>default_dilution_isotherm</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>600</v>
-      </c>
+      <c r="B11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1362,58 +1409,8 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>solid:&lt;矿物&gt; 行为固液比 m/V (g/L)，矿物名与 Data 表一致；未列的矿物按 mg/L(悬浮液) 处理</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>solid:δ-MnO₂</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>solid:Rancieite</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>solid:Acid birnessite</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>solid:Alkaline birnessite</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>solid:Feroxyhyte</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>0.5</v>
+          <t>solid:&lt;吸附剂&gt; 行为固液比 m/V (g/L)，名称与 Data 表一致；未列的按 mg/L(悬浮液) 处理</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/templates/吸附数据模板.xlsx
+++ b/templates/吸附数据模板.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -881,7 +881,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>固液比 m/V。留空取 Settings 中该矿物的值</t>
+          <t>固液比 m/V。留空取 Settings 中该吸附剂的值</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1064,12 +1064,12 @@
         <v>0.01</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="n">
-        <v>7.82</v>
+        <v>0.34</v>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
@@ -1109,12 +1109,12 @@
         <v>0.01</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="n">
-        <v>7.65</v>
+        <v>1.12</v>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="n">
@@ -1127,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="b">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Mineral B</t>
+          <t>Mineral A</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
         <v>0.01</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="n">
-        <v>5.1</v>
+        <v>2.58</v>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="n">
@@ -1182,7 +1182,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>kinetics</t>
+          <t>isotherm</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1201,19 +1201,17 @@
       <c r="E5" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>24</v>
-      </c>
+      <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="n">
-        <v>102.4</v>
-      </c>
+      <c r="H5" s="2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>2</v>
@@ -1229,7 +1227,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>edge</t>
+          <t>isotherm</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1249,11 +1247,9 @@
         <v>10</v>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="n">
-        <v>1.25</v>
+        <v>4.41</v>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="n">
@@ -1266,10 +1262,754 @@
         <v>2</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>isotherm</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Mineral A</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>isotherm</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Mineral B</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>isotherm</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Mineral B</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>isotherm</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Mineral B</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>kinetics</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Mineral A</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>kinetics</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Mineral A</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>kinetics</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Mineral A</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>kinetics</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Mineral A</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>kinetics</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Mineral A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>kinetics</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Mineral A</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Mineral A</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Mineral A</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Mineral A</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Mineral A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Mineral A</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Mineral A</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0.01 M NaCl</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="b">
         <v>0</v>
       </c>
     </row>
